--- a/train_results.xlsx
+++ b/train_results.xlsx
@@ -14,6 +14,7 @@
     <sheet name="prob(0.5)" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="prob(0.6)" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="prob(0.7)" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="combined" sheetId="7" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="25">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -63,9 +64,21 @@
     <t xml:space="preserve">DenseNet201</t>
   </si>
   <si>
+    <t xml:space="preserve">VGG16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VGG19</t>
+  </si>
+  <si>
     <t xml:space="preserve">dm</t>
   </si>
   <si>
+    <t xml:space="preserve">FREQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recall</t>
   </si>
   <si>
@@ -73,6 +86,21 @@
   </si>
   <si>
     <t xml:space="preserve">F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valid+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valid-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precision</t>
   </si>
 </sst>
 </file>
@@ -112,12 +140,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -154,7 +188,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -167,7 +201,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -188,8 +230,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.89"/>
   </cols>
@@ -239,7 +281,7 @@
       <c r="F2" s="0" t="n">
         <v>2968</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="0" t="n">
         <v>0.502084030518456</v>
       </c>
       <c r="H2" s="0" t="n">
@@ -265,7 +307,7 @@
       <c r="F3" s="0" t="n">
         <v>3002</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="0" t="n">
         <v>0.503706974169565</v>
       </c>
       <c r="H3" s="0" t="n">
@@ -291,7 +333,7 @@
       <c r="F4" s="0" t="n">
         <v>2974</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="0" t="n">
         <v>0.501822612588368</v>
       </c>
       <c r="H4" s="0" t="n">
@@ -300,79 +342,183 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>16981</v>
+        <v>16987</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>17019</v>
+        <v>17013</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>3019</v>
+        <v>3013</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>2981</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0.502804518219024</v>
+        <v>2987</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.512441589718773</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>16972</v>
+        <v>16983</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>17028</v>
+        <v>17017</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>3028</v>
+        <v>3017</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>2972</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0.502050775384146</v>
+        <v>2983</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.514829308740676</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>16981</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>17019</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>3019</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>2981</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.502804518219024</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>16972</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>17028</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>3028</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>2972</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0.502050775384146</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>16943</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>17057</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>3057</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>2943</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0.500262489867589</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>16943</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>17057</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>3057</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>2943</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0.500262489867589</v>
-      </c>
-      <c r="H7" s="0" t="n">
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>17030</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>16070</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>2970</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>3030</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0.510409388277266</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>16980</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>17020</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>3020</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>2980</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>0.506366344671401</v>
+      </c>
+      <c r="H11" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -392,60 +538,67 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>54.58</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>99.89</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>70.59</v>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
+      <c r="B3" s="2" t="n">
+        <v>54.58</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>99.89</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>99.32</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>99.64</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>99.48</v>
       </c>
     </row>
@@ -453,71 +606,123 @@
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+      <c r="B4" s="2" t="n">
+        <v>66.73</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>66.73</v>
+        <v>99.91</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>99.91</v>
+        <v>80.02</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>80.02</v>
+        <v>99.11</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>99.5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>79.08</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>99.11</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>99.88</v>
+        <v>99.94</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>88.3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>99.5</v>
+        <v>98.71</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>99.17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>63.42</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>79.08</v>
+        <v>95.48</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>99.94</v>
+        <v>76.21</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>88.3</v>
+        <v>99.07</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>97.86</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>98.37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>77.96</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>98.71</v>
+        <v>95.65</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>99.64</v>
+        <v>85.9</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>99.17</v>
-      </c>
+        <v>97.99</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>98.46</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>97.99</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -533,60 +738,68 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>99.97</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>69.24</v>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
+      <c r="B3" s="2" t="n">
+        <v>52.96</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>69.24</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>99.19</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>99.71</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>99.45</v>
       </c>
     </row>
@@ -594,71 +807,108 @@
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+      <c r="B4" s="2" t="n">
+        <v>65.41</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>65.41</v>
+        <v>99.95</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>99.95</v>
+        <v>79.07</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>79.07</v>
+        <v>98.89</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>99.4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>74.91</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>98.89</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>99.92</v>
+        <v>99.89</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>85.65</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>99.4</v>
+        <v>98.26</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>98.99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>61.07</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>74.91</v>
+        <v>97.35</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>99.89</v>
+        <v>75.06</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>85.65</v>
+        <v>98.5</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>98.46</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>98.48</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>70.51</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>98.26</v>
+        <v>97.17</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>99.73</v>
+        <v>81.72</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>98.99</v>
-      </c>
+        <v>97.09</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>98.07</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -674,60 +924,68 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>51.55</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>68.03</v>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
+      <c r="B3" s="2" t="n">
+        <v>51.55</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>68.03</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>99.11</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>99.77</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>99.44</v>
       </c>
     </row>
@@ -735,71 +993,108 @@
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+      <c r="B4" s="2" t="n">
+        <v>64.32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>64.32</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>100</v>
+        <v>78.28</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>78.28</v>
+        <v>98.72</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>99.32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>71.02</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>98.72</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>99.92</v>
+        <v>99.98</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>83.05</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>99.32</v>
+        <v>97.67</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>98.73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>59.56</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>71.02</v>
+        <v>98.19</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>99.98</v>
+        <v>74.15</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>83.05</v>
+        <v>97.75</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>98.37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>65.37</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>97.67</v>
+        <v>98.24</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>99.8</v>
+        <v>78.5</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>98.73</v>
-      </c>
+        <v>96.74</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>98.06</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -815,60 +1110,68 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>66.95</v>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
+      <c r="B3" s="2" t="n">
+        <v>50.32</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>66.95</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>98.98</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>99.83</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>99.4</v>
       </c>
     </row>
@@ -876,71 +1179,108 @@
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+      <c r="B4" s="2" t="n">
+        <v>63.15</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>63.15</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>100</v>
+        <v>77.41</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>77.41</v>
+        <v>98.63</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>99.28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>67.51</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>98.63</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>99.94</v>
+        <v>100</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>80.61</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>99.28</v>
+        <v>97.27</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>99.82</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>98.53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>57.79</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>67.51</v>
+        <v>98.74</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>100</v>
+        <v>72.91</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>80.61</v>
+        <v>97.1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>99.32</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>98.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>61.96</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>97.27</v>
+        <v>98.99</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>99.82</v>
+        <v>76.22</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>98.53</v>
-      </c>
+        <v>96.32</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>97.94</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -956,27 +1296,222 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>65.66</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>99.34</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>98.38</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>99.17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>77.77</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>98.25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>99.23</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>94.82</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>99.51</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>97.11</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>74.16</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>97.71</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -984,102 +1519,443 @@
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>65.66</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>98.78</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>99.83</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>99.34</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>61.91</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>76.48</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>98.38</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>99.97</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>99.17</v>
-      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>63.63</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>77.77</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>99.86</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>98.25</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>16926</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>17074</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3074</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2926</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.498721112754751</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>90.58</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>99.93</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>95.03</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/train_results.xlsx
+++ b/train_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Train overview" sheetId="1" state="visible" r:id="rId2"/>
@@ -188,7 +188,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -201,7 +201,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -211,6 +211,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -231,7 +235,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.89"/>
   </cols>
@@ -539,7 +543,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -739,7 +743,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -925,7 +929,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -1111,7 +1115,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -1297,7 +1301,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -1477,7 +1481,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1566,21 +1570,39 @@
       <c r="K4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="C5" s="6" t="n">
+        <v>17006</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>16994</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2994</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>3006</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0.503899073822701</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>73.81</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>84.93</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">

--- a/train_results.xlsx
+++ b/train_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Train overview" sheetId="1" state="visible" r:id="rId2"/>
@@ -188,7 +188,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -201,12 +201,16 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -235,7 +239,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.89"/>
   </cols>
@@ -397,132 +401,132 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="4" t="n">
         <v>16981</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="4" t="n">
         <v>17019</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="4" t="n">
         <v>3019</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="4" t="n">
         <v>2981</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="4" t="n">
         <v>0.502804518219024</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="4" t="n">
         <v>16972</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="4" t="n">
         <v>17028</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="4" t="n">
         <v>3028</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="4" t="n">
         <v>2972</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.502050775384146</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="4" t="n">
         <v>16943</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="4" t="n">
         <v>17057</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="4" t="n">
         <v>3057</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="4" t="n">
         <v>2943</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="4" t="n">
         <v>0.500262489867589</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="4" t="n">
         <v>17030</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="4" t="n">
         <v>16070</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="4" t="n">
         <v>2970</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="4" t="n">
         <v>3030</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="4" t="n">
         <v>0.510409388277266</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="4" t="n">
         <v>16980</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="4" t="n">
         <v>17020</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="4" t="n">
         <v>3020</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="4" t="n">
         <v>2980</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="4" t="n">
         <v>0.506366344671401</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -543,22 +547,22 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -625,7 +629,7 @@
       <c r="F4" s="2" t="n">
         <v>99.88</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="3" t="n">
         <v>99.5</v>
       </c>
     </row>
@@ -639,7 +643,7 @@
       <c r="C5" s="2" t="n">
         <v>99.94</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>88.3</v>
       </c>
       <c r="E5" s="2" t="n">
@@ -743,23 +747,23 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -803,7 +807,7 @@
       <c r="F3" s="2" t="n">
         <v>99.71</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="3" t="n">
         <v>99.45</v>
       </c>
     </row>
@@ -840,7 +844,7 @@
       <c r="C5" s="2" t="n">
         <v>99.89</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>85.65</v>
       </c>
       <c r="E5" s="2" t="n">
@@ -929,23 +933,23 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -989,7 +993,7 @@
       <c r="F3" s="2" t="n">
         <v>99.77</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="3" t="n">
         <v>99.44</v>
       </c>
     </row>
@@ -1026,7 +1030,7 @@
       <c r="C5" s="2" t="n">
         <v>99.98</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>83.05</v>
       </c>
       <c r="E5" s="2" t="n">
@@ -1115,23 +1119,23 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -1175,7 +1179,7 @@
       <c r="F3" s="2" t="n">
         <v>99.83</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="3" t="n">
         <v>99.4</v>
       </c>
     </row>
@@ -1212,7 +1216,7 @@
       <c r="C5" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>80.61</v>
       </c>
       <c r="E5" s="2" t="n">
@@ -1301,7 +1305,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -1313,7 +1317,7 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1359,7 +1363,7 @@
       <c r="F3" s="2" t="n">
         <v>99.83</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="3" t="n">
         <v>99.34</v>
       </c>
     </row>
@@ -1396,7 +1400,7 @@
       <c r="C5" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>77.77</v>
       </c>
       <c r="E5" s="2" t="n">
@@ -1481,7 +1485,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1570,37 +1574,37 @@
       <c r="K4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="2" t="n">
         <v>17006</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="2" t="n">
         <v>16994</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="2" t="n">
         <v>2994</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="2" t="n">
         <v>3006</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.503899073822701</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="2" t="n">
         <v>73.81</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="2" t="n">
         <v>84.93</v>
       </c>
     </row>
@@ -1748,15 +1752,33 @@
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="C13" s="2" t="n">
+        <v>17031</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>16969</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2969</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>3031</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.50509884430373</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>68.35</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>81.2</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -1765,32 +1787,68 @@
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="C14" s="2" t="n">
+        <v>16950</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>17050</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3050</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>2950</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.499920884503963</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>90.83</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
+      <c r="C15" s="7" t="n">
+        <v>16957</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>17043</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>3043</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>2957</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0.500362905416083</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>65.07</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>78.8</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
@@ -1799,15 +1857,33 @@
       <c r="B16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="C16" s="2" t="n">
+        <v>17028</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>16972</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2972</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>3028</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0.505012486209261</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>67.54</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>99.89</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>80.59</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">

--- a/train_results.xlsx
+++ b/train_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Train overview" sheetId="1" state="visible" r:id="rId2"/>
@@ -140,7 +140,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,13 +153,26 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFD7"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -188,7 +201,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -213,11 +226,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -230,6 +259,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFD7"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -239,7 +328,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.89"/>
   </cols>
@@ -277,24 +366,6 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>16968</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>17032</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>3032</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>2968</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>0.502084030518456</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -303,24 +374,6 @@
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>17002</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>16998</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>2998</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>3002</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0.503706974169565</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -329,24 +382,6 @@
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>16974</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>17026</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>3026</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>2974</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0.501822612588368</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -355,24 +390,6 @@
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>16987</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>17013</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>3013</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>2987</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0.512441589718773</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -381,24 +398,6 @@
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>16983</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>17017</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>3017</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>2983</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0.514829308740676</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
@@ -407,24 +406,12 @@
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>16981</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>17019</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>3019</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>2981</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0.502804518219024</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
@@ -433,24 +420,12 @@
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>16972</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>17028</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>3028</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>2972</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>0.502050775384146</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
@@ -459,24 +434,12 @@
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>16943</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>17057</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>3057</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>2943</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0.500262489867589</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
@@ -485,24 +448,12 @@
       <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>17030</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>16070</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>2970</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>3030</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0.510409388277266</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
@@ -511,24 +462,12 @@
       <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>16980</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>17020</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>3020</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>2980</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0.506366344671401</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -547,7 +486,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -591,116 +530,56 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>54.58</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>99.89</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>70.59</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>99.32</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>99.64</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>99.48</v>
-      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>66.73</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>99.91</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>80.02</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>99.11</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>99.88</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>99.5</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>79.08</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>99.94</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>98.71</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>99.64</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>99.17</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>63.42</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>95.48</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>76.21</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>99.07</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>97.86</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>98.37</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>77.96</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>95.65</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>85.9</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>97.99</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>98.46</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>97.99</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -747,7 +626,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -792,116 +671,56 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>99.97</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>69.24</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>99.19</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>99.71</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>99.45</v>
-      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>65.41</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>99.95</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>79.07</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>98.89</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>99.92</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>99.4</v>
-      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>99.89</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>85.65</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>98.26</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>99.73</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>98.99</v>
-      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>61.07</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>97.35</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>98.46</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>98.48</v>
-      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>70.51</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>97.17</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>81.72</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>97.09</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>99.08</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>98.07</v>
-      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -933,7 +752,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -978,116 +797,56 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>51.55</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>68.03</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>99.11</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>99.77</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>99.44</v>
-      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>64.32</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>78.28</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>98.72</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>99.92</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>99.32</v>
-      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>71.02</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>99.98</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>83.05</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>97.67</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>98.73</v>
-      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>59.56</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>98.19</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>74.15</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>97.75</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>98.37</v>
-      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>98.24</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>96.74</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>99.41</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>98.06</v>
-      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -1119,7 +878,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -1164,116 +923,56 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>66.95</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>98.98</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>99.83</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>99.4</v>
-      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>77.41</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>98.63</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>99.94</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>99.28</v>
-      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>67.51</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>80.61</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>97.27</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>99.82</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>98.53</v>
-      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>57.79</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>98.74</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>72.91</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>97.1</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>99.32</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>98.2</v>
-      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>61.96</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>98.99</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>76.22</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>96.32</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>99.61</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>97.94</v>
-      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -1305,21 +1004,23 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="6" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7" t="s">
         <v>16</v>
       </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -1348,116 +1049,56 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>65.66</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>98.78</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>99.83</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>99.34</v>
-      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>61.91</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>76.48</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>98.38</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>99.97</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>99.17</v>
-      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>63.63</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>77.77</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>99.86</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>98.25</v>
-      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>56.12</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>99.23</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>94.82</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>99.51</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>97.11</v>
-      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>99.44</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>74.16</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>95.77</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>99.73</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>97.71</v>
-      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -1469,6 +1110,10 @@
       <c r="A12" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1485,40 +1130,40 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1580,135 +1225,117 @@
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>17006</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>16994</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>2994</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3006</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.503899073822701</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>73.81</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>84.93</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -1717,33 +1344,15 @@
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>16926</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>17074</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>3074</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>2926</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0.498721112754751</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>90.58</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>99.93</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>95.03</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -1752,33 +1361,15 @@
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>17031</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>16969</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>2969</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>3031</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0.50509884430373</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>68.35</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>81.2</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -1787,188 +1378,134 @@
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>16950</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>17050</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>3050</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>2950</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0.499920884503963</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>83.19</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>90.83</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>16957</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>17043</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>3043</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>2957</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>0.500362905416083</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>65.07</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>99.88</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>78.8</v>
-      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>17028</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>16972</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>2972</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>3028</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0.505012486209261</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>67.54</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>99.89</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>80.59</v>
-      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
@@ -2039,21 +1576,21 @@
       <c r="K25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/train_results.xlsx
+++ b/train_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Train overview" sheetId="1" state="visible" r:id="rId2"/>
@@ -201,7 +201,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -223,14 +223,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -328,7 +320,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.89"/>
   </cols>
@@ -366,6 +358,24 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="C2" s="0" t="n">
+        <v>16968</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>17032</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>3032</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>2968</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.502014754310487</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -374,6 +384,24 @@
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="C3" s="0" t="n">
+        <v>16978</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>17022</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>3022</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>2978</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.502216119141806</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -382,6 +410,24 @@
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="C4" s="0" t="n">
+        <v>16970</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>17030</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>3030</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>2970</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.501611094626169</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -390,6 +436,24 @@
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="C5" s="0" t="n">
+        <v>16989</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>17011</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>3011</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>2989</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.512986568704484</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -398,6 +462,24 @@
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="C6" s="0" t="n">
+        <v>16988</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>17012</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>3012</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>2988</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.514079347489372</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
@@ -406,12 +488,24 @@
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="C7" s="4" t="n">
+        <v>17011</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>16989</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2989</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>3011</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.504649150939215</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
@@ -486,7 +580,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -530,31 +624,55 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="B3" s="2" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>99.43</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>99.33</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>99.38</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="B4" s="2" t="n">
+        <v>65.77</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>79.32</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="6"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="6"/>
+      <c r="B5" s="2" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>99.71</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>92.65</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -563,9 +681,15 @@
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="2" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>82.74</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -574,9 +698,15 @@
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="B7" s="2" t="n">
+        <v>72.49</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>81.65</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -626,7 +756,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -671,56 +801,92 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="2" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>99.23</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>99.62</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>99.43</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="B4" s="2" t="n">
+        <v>65.32</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>78.99</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="B5" s="2" t="n">
+        <v>84.35</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>99.82</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>91.44</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="B6" s="2" t="n">
+        <v>65.4</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>77.96</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="B7" s="2" t="n">
+        <v>67.35</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -752,7 +918,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -797,56 +963,92 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="2" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>68.48</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>98.96</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>99.79</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>99.37</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="B4" s="2" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="B5" s="2" t="n">
+        <v>82.65</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>99.82</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>90.43</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="B6" s="2" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>98.02</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>73.36</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="B7" s="2" t="n">
+        <v>62.94</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>97.02</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>76.34</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -878,7 +1080,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -923,56 +1125,92 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="2" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>98.74</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>99.3</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="B4" s="2" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>78.1</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="B5" s="2" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="B6" s="2" t="n">
+        <v>53.54</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="B7" s="2" t="n">
+        <v>60.31</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>74.67</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -1004,23 +1242,23 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -1049,56 +1287,92 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="2" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>66.31</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>98.51</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>99.21</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="B4" s="2" t="n">
+        <v>63.07</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>77.35</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="B5" s="2" t="n">
+        <v>78.18</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>87.73</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="B6" s="2" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>99.34</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>66.21</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="B7" s="2" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>98.9</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>72.97</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -1130,40 +1404,40 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1236,106 +1510,106 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -1406,106 +1680,106 @@
       <c r="K15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
@@ -1576,21 +1850,21 @@
       <c r="K25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/train_results.xlsx
+++ b/train_results.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="26">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t xml:space="preserve">F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99l.53</t>
   </si>
   <si>
     <t xml:space="preserve">valid+</t>
@@ -514,12 +517,24 @@
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="C8" s="4" t="n">
+        <v>17032</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>16968</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>2968</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>3032</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.505413048324131</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
@@ -528,12 +543,24 @@
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="C9" s="4" t="n">
+        <v>17020</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>16980</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>2980</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>3020</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.504540154858241</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
@@ -656,9 +683,15 @@
       <c r="D4" s="2" t="n">
         <v>79.32</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="2" t="n">
+        <v>95.74</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>97.67</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -673,9 +706,15 @@
       <c r="D5" s="2" t="n">
         <v>92.65</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="2" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>99.45</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -833,9 +872,15 @@
       <c r="D4" s="2" t="n">
         <v>78.99</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="2" t="n">
+        <v>94.9</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>97.26</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -850,9 +895,15 @@
       <c r="D5" s="2" t="n">
         <v>91.44</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="2" t="n">
+        <v>99.14</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>99.44</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -995,9 +1046,15 @@
       <c r="D4" s="2" t="n">
         <v>78.5</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="2" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>96.87</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -1012,9 +1069,15 @@
       <c r="D5" s="2" t="n">
         <v>90.43</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="2" t="n">
+        <v>98.9</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>99.82</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>99.36</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -1157,9 +1220,15 @@
       <c r="D4" s="2" t="n">
         <v>78.1</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="2" t="n">
+        <v>93.07</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.79</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>96.31</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -1174,9 +1243,15 @@
       <c r="D5" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="2" t="n">
+        <v>98.51</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>99.85</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>99.18</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -1319,9 +1394,15 @@
       <c r="D4" s="2" t="n">
         <v>77.35</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="2" t="n">
+        <v>92.15</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>95.84</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -1336,9 +1417,15 @@
       <c r="D5" s="2" t="n">
         <v>87.73</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="2" t="n">
+        <v>97.93</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>98.89</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -1420,22 +1507,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>19</v>

--- a/train_results.xlsx
+++ b/train_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Train overview" sheetId="1" state="visible" r:id="rId2"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="25">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t xml:space="preserve">F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99l.53</t>
   </si>
   <si>
     <t xml:space="preserve">valid+</t>
@@ -323,7 +320,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.89"/>
   </cols>
@@ -361,24 +358,6 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>16968</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>17032</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>3032</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>2968</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>0.502014754310487</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -387,24 +366,6 @@
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>16978</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>17022</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>3022</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>2978</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0.502216119141806</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -413,24 +374,6 @@
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>16970</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>17030</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>3030</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>2970</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0.501611094626169</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -439,24 +382,6 @@
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>16989</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>17011</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>3011</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>2989</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0.512986568704484</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -465,24 +390,6 @@
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>16988</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>17012</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>3012</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>2988</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0.514079347489372</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
@@ -491,24 +398,12 @@
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>17011</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>16989</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>2989</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>3011</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0.504649150939215</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
@@ -517,24 +412,12 @@
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>17032</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>16968</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>2968</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>3032</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>0.505413048324131</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
@@ -543,24 +426,12 @@
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>17020</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>16980</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>2980</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>3020</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0.504540154858241</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
@@ -607,7 +478,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -651,84 +522,42 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>54.95</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>99.97</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>70.92</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>99.43</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>99.33</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>99.38</v>
-      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>65.77</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>99.91</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>79.32</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>95.74</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>99.67</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>97.67</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>86.52</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>99.71</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>92.65</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>99.37</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>99.45</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>74.14</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>93.58</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>82.74</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -737,15 +566,9 @@
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>72.49</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>93.44</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>81.65</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -795,7 +618,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -840,84 +663,42 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>53.41</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>99.23</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>99.62</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>99.43</v>
-      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>65.32</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>99.91</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>78.99</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>94.9</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>97.26</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>84.35</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>99.82</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>91.44</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>99.14</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>99.73</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>99.44</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>65.4</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>77.96</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -926,15 +707,9 @@
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>67.35</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>95.53</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>79</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -969,7 +744,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -1014,84 +789,42 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>68.48</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>98.96</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>99.79</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>99.37</v>
-      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>64.62</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>99.98</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>94.13</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>99.78</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>96.87</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>82.65</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>99.82</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>90.43</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>98.9</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>99.82</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>99.36</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>58.61</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>98.02</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>73.36</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -1100,15 +833,9 @@
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>62.94</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>97.02</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>76.34</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1143,7 +870,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -1188,84 +915,42 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>50.92</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>67.48</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>98.74</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>99.86</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>99.3</v>
-      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>64.08</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>99.98</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>78.1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>93.07</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>99.79</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>96.31</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>80.27</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>99.87</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>98.51</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>99.85</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>99.18</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>53.54</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>98.92</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>69.48</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -1274,15 +959,9 @@
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>60.31</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>74.67</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1317,7 +996,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
@@ -1362,84 +1041,42 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>66.31</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>98.51</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>99.91</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>99.21</v>
-      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>63.07</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>77.35</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>92.15</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>99.84</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>95.84</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>78.18</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>99.94</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>87.73</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>97.93</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>99.88</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>98.89</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>49.65</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>99.34</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>66.21</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -1448,15 +1085,9 @@
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>57.82</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>98.9</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>72.97</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1491,7 +1122,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
@@ -1507,22 +1138,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>19</v>

--- a/train_results.xlsx
+++ b/train_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hogdo\git\fetch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E99BDF2-6BC4-4AA6-9709-1AE60B54DA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AA443A-0C62-41E6-8D29-77B3AB361408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12084" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="11148" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Train overview" sheetId="1" r:id="rId1"/>
@@ -171,9 +171,6 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -194,6 +191,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -604,36 +604,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C2">
@@ -656,10 +656,10 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C3">
@@ -682,10 +682,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C4">
@@ -708,10 +708,10 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C5">
@@ -734,82 +734,160 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="C6">
+        <v>16929</v>
+      </c>
+      <c r="D6">
+        <v>17071</v>
+      </c>
+      <c r="E6">
+        <v>3071</v>
+      </c>
+      <c r="F6">
+        <v>2929</v>
+      </c>
+      <c r="G6">
+        <v>0.54781701120119197</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="C7" s="4">
+        <v>17018</v>
+      </c>
+      <c r="D7" s="4">
+        <v>16982</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2982</v>
+      </c>
+      <c r="F7" s="4">
+        <v>3018</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.50474521943501005</v>
+      </c>
+      <c r="H7" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="C8" s="4">
+        <v>17021</v>
+      </c>
+      <c r="D8" s="4">
+        <v>16979</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2979</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3021</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.50544260465909496</v>
+      </c>
+      <c r="H8" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="C9" s="4">
+        <v>17008</v>
+      </c>
+      <c r="D9" s="4">
+        <v>16992</v>
+      </c>
+      <c r="E9" s="4">
+        <v>2992</v>
+      </c>
+      <c r="F9" s="4">
+        <v>3008</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.50408383778163302</v>
+      </c>
+      <c r="H9" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="C10" s="4">
+        <v>16936</v>
+      </c>
+      <c r="D10" s="4">
+        <v>17064</v>
+      </c>
+      <c r="E10" s="4">
+        <v>3064</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2936</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.50394623856695797</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="C11" s="4">
+        <v>16982</v>
+      </c>
+      <c r="D11" s="4">
+        <v>17018</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3018</v>
+      </c>
+      <c r="F11" s="4">
+        <v>2982</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.50643191261897003</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -830,142 +908,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>59.95</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>98.42</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>74.510000000000005</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>67.47</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>96.96</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>79.569999999999993</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>62.7</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>98.1</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>76.5</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>61.87</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>77.12</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>68.66</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -990,128 +1068,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>58.28</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>98.88</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>73.430000000000007</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>67.02</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>97.7</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>79.5</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>61.96</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>98.66</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>76.12</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>54.46</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>83.01</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>65.77</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
+      <c r="A10" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
+      <c r="A12" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1136,128 +1214,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>56.99</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>99.09</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>72.36</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>66.52</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>98.38</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>79.37</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>61.16</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>99.15</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>76.12</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>47.99</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>86.9</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>61.83</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
+      <c r="A10" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
+      <c r="A12" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1282,128 +1360,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>55.55</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>99.33</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>71.25</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>65.88</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>98.7</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>79.010000000000005</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>60.23</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>99.48</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>75.040000000000006</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>44.48</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>91.03</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>59.76</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
+      <c r="A10" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
+      <c r="A12" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1428,128 +1506,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>54.19</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>99.59</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>70.180000000000007</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>64.78</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>99.04</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>78.33</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>59.24</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>99.62</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>74.3</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>42.99</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>94.43</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>59.08</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
+      <c r="A10" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
+      <c r="A12" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1571,464 +1649,464 @@
   <sheetFormatPr defaultColWidth="11.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>

--- a/train_results.xlsx
+++ b/train_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hogdo\git\fetch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AA443A-0C62-41E6-8D29-77B3AB361408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2247413-0FDF-43AF-A4DD-5F6ED7F0954A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="11148" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Train overview" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,6 +144,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFD7"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -168,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -192,8 +216,20 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -268,6 +304,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -908,16 +947,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -955,9 +994,15 @@
       <c r="D3" s="2">
         <v>74.510000000000005</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="E3" s="2">
+        <v>99.49</v>
+      </c>
+      <c r="F3" s="2">
+        <v>99.49</v>
+      </c>
+      <c r="G3" s="2">
+        <v>99.49</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -972,9 +1017,15 @@
       <c r="D4" s="2">
         <v>79.569999999999993</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="2">
+        <v>98.69</v>
+      </c>
+      <c r="F4" s="2">
+        <v>99.89</v>
+      </c>
+      <c r="G4" s="2">
+        <v>99.29</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -989,9 +1040,15 @@
       <c r="D5" s="2">
         <v>76.5</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="2">
+        <v>96.14</v>
+      </c>
+      <c r="F5" s="2">
+        <v>99.92</v>
+      </c>
+      <c r="G5" s="2">
+        <v>98</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1006,20 +1063,38 @@
       <c r="D6" s="2">
         <v>68.66</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="E6" s="2">
+        <v>98.74</v>
+      </c>
+      <c r="F6" s="2">
+        <v>98</v>
+      </c>
+      <c r="G6" s="2">
+        <v>98.37</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="B7" s="2">
+        <v>75.27</v>
+      </c>
+      <c r="C7" s="2">
+        <v>70.13</v>
+      </c>
+      <c r="D7" s="2">
+        <v>72.61</v>
+      </c>
+      <c r="E7" s="2">
+        <v>97.28</v>
+      </c>
+      <c r="F7" s="2">
+        <v>97.89</v>
+      </c>
+      <c r="G7" s="2">
+        <v>97.58</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -1069,16 +1144,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1116,9 +1191,15 @@
       <c r="D3" s="2">
         <v>73.430000000000007</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="E3" s="2">
+        <v>99.14</v>
+      </c>
+      <c r="F3" s="2">
+        <v>99.68</v>
+      </c>
+      <c r="G3" s="2">
+        <v>99.41</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1133,9 +1214,15 @@
       <c r="D4" s="2">
         <v>79.5</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="2">
+        <v>98.36</v>
+      </c>
+      <c r="F4" s="2">
+        <v>99.91</v>
+      </c>
+      <c r="G4" s="2">
+        <v>99.13</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1150,9 +1237,15 @@
       <c r="D5" s="2">
         <v>76.12</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="2">
+        <v>95.17</v>
+      </c>
+      <c r="F5" s="2">
+        <v>99.97</v>
+      </c>
+      <c r="G5" s="2">
+        <v>97.51</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1167,20 +1260,38 @@
       <c r="D6" s="2">
         <v>65.77</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="E6" s="2">
+        <v>97.85</v>
+      </c>
+      <c r="F6" s="2">
+        <v>98.79</v>
+      </c>
+      <c r="G6" s="2">
+        <v>98.32</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="B7" s="2">
+        <v>63.57</v>
+      </c>
+      <c r="C7" s="2">
+        <v>73.95</v>
+      </c>
+      <c r="D7" s="2">
+        <v>68.37</v>
+      </c>
+      <c r="E7" s="2">
+        <v>96.95</v>
+      </c>
+      <c r="F7" s="2">
+        <v>99.05</v>
+      </c>
+      <c r="G7" s="2">
+        <v>97.99</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -1215,16 +1326,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1250,7 +1361,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2">
@@ -1262,26 +1373,38 @@
       <c r="D3" s="2">
         <v>72.36</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="E3" s="9">
+        <v>98.84</v>
+      </c>
+      <c r="F3" s="9">
+        <v>99.73</v>
+      </c>
+      <c r="G3" s="9">
+        <v>99.28</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="9">
         <v>66.52</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="9">
         <v>98.38</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="9">
         <v>79.37</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="2">
+        <v>98.03</v>
+      </c>
+      <c r="F4" s="2">
+        <v>99.91</v>
+      </c>
+      <c r="G4" s="2">
+        <v>98.96</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1296,9 +1419,15 @@
       <c r="D5" s="2">
         <v>76.12</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="2">
+        <v>94</v>
+      </c>
+      <c r="F5" s="2">
+        <v>99.97</v>
+      </c>
+      <c r="G5" s="2">
+        <v>96.89</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1313,20 +1442,38 @@
       <c r="D6" s="2">
         <v>61.83</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="E6" s="2">
+        <v>96.43</v>
+      </c>
+      <c r="F6" s="2">
+        <v>99.26</v>
+      </c>
+      <c r="G6" s="2">
+        <v>97.82</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="B7" s="2">
+        <v>56.08</v>
+      </c>
+      <c r="C7" s="2">
+        <v>81.17</v>
+      </c>
+      <c r="D7" s="2">
+        <v>66.33</v>
+      </c>
+      <c r="E7" s="2">
+        <v>96.55</v>
+      </c>
+      <c r="F7" s="2">
+        <v>99.54</v>
+      </c>
+      <c r="G7" s="2">
+        <v>98.02</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -1361,16 +1508,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1408,9 +1555,15 @@
       <c r="D3" s="2">
         <v>71.25</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="E3" s="2">
+        <v>98.48</v>
+      </c>
+      <c r="F3" s="2">
+        <v>99.82</v>
+      </c>
+      <c r="G3" s="2">
+        <v>99.15</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1425,9 +1578,15 @@
       <c r="D4" s="2">
         <v>79.010000000000005</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="2">
+        <v>97.64</v>
+      </c>
+      <c r="F4" s="2">
+        <v>99.91</v>
+      </c>
+      <c r="G4" s="2">
+        <v>98.76</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1442,9 +1601,15 @@
       <c r="D5" s="2">
         <v>75.040000000000006</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="2">
+        <v>92.71</v>
+      </c>
+      <c r="F5" s="2">
+        <v>99.97</v>
+      </c>
+      <c r="G5" s="2">
+        <v>96.2</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1459,20 +1624,38 @@
       <c r="D6" s="2">
         <v>59.76</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="E6" s="2">
+        <v>93.98</v>
+      </c>
+      <c r="F6" s="2">
+        <v>99.49</v>
+      </c>
+      <c r="G6" s="2">
+        <v>96.66</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="B7" s="2">
+        <v>49.71</v>
+      </c>
+      <c r="C7" s="2">
+        <v>87.14</v>
+      </c>
+      <c r="D7" s="2">
+        <v>63.13</v>
+      </c>
+      <c r="E7" s="2">
+        <v>96.16</v>
+      </c>
+      <c r="F7" s="2">
+        <v>99.77</v>
+      </c>
+      <c r="G7" s="2">
+        <v>97.93</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -1507,16 +1690,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1554,9 +1737,15 @@
       <c r="D3" s="2">
         <v>70.180000000000007</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="E3" s="2">
+        <v>98.12</v>
+      </c>
+      <c r="F3" s="2">
+        <v>99.83</v>
+      </c>
+      <c r="G3" s="2">
+        <v>98.97</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1571,9 +1760,15 @@
       <c r="D4" s="2">
         <v>78.33</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="2">
+        <v>96.92</v>
+      </c>
+      <c r="F4" s="2">
+        <v>99.95</v>
+      </c>
+      <c r="G4" s="2">
+        <v>98.42</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1588,9 +1783,15 @@
       <c r="D5" s="2">
         <v>74.3</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="2">
+        <v>91.15</v>
+      </c>
+      <c r="F5" s="2">
+        <v>99.98</v>
+      </c>
+      <c r="G5" s="2">
+        <v>95.36</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1605,20 +1806,38 @@
       <c r="D6" s="2">
         <v>59.08</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="E6" s="2">
+        <v>90.77</v>
+      </c>
+      <c r="F6" s="2">
+        <v>99.59</v>
+      </c>
+      <c r="G6" s="2">
+        <v>94.98</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="B7" s="2">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="C7" s="2">
+        <v>90.94</v>
+      </c>
+      <c r="D7" s="2">
+        <v>51.27</v>
+      </c>
+      <c r="E7" s="2">
+        <v>95.77</v>
+      </c>
+      <c r="F7" s="2">
+        <v>99.83</v>
+      </c>
+      <c r="G7" s="2">
+        <v>97.76</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -1684,21 +1903,39 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="C2" s="13">
+        <v>16986</v>
+      </c>
+      <c r="D2" s="13">
+        <v>17014</v>
+      </c>
+      <c r="E2" s="13">
+        <v>3014</v>
+      </c>
+      <c r="F2" s="13">
+        <v>2986</v>
+      </c>
+      <c r="G2" s="13">
+        <v>32</v>
+      </c>
+      <c r="H2" s="13">
+        <v>0.50250986551350696</v>
+      </c>
+      <c r="I2" s="13">
+        <v>84.45</v>
+      </c>
+      <c r="J2" s="13">
+        <v>99.98</v>
+      </c>
+      <c r="K2" s="13">
+        <v>91.56</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -1707,15 +1944,33 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="C3" s="2">
+        <v>17081</v>
+      </c>
+      <c r="D3" s="2">
+        <v>16919</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2919</v>
+      </c>
+      <c r="F3" s="2">
+        <v>3081</v>
+      </c>
+      <c r="G3" s="2">
+        <v>512</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.50850872061354002</v>
+      </c>
+      <c r="I3" s="2">
+        <v>78.78</v>
+      </c>
+      <c r="J3" s="2">
+        <v>99.94</v>
+      </c>
+      <c r="K3" s="2">
+        <v>88.11</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1724,15 +1979,33 @@
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="C4" s="2">
+        <v>16919</v>
+      </c>
+      <c r="D4" s="2">
+        <v>17081</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3081</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2919</v>
+      </c>
+      <c r="G4" s="2">
+        <v>128</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.49808965544117201</v>
+      </c>
+      <c r="I4" s="2">
+        <v>74.05</v>
+      </c>
+      <c r="J4" s="2">
+        <v>99.94</v>
+      </c>
+      <c r="K4" s="2">
+        <v>85.07</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1741,15 +2014,33 @@
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="C5" s="2">
+        <v>16979</v>
+      </c>
+      <c r="D5" s="2">
+        <v>17021</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3021</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2979</v>
+      </c>
+      <c r="G5" s="2">
+        <v>256</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.50252008517371805</v>
+      </c>
+      <c r="I5" s="2">
+        <v>67.66</v>
+      </c>
+      <c r="J5" s="2">
+        <v>99.78</v>
+      </c>
+      <c r="K5" s="2">
+        <v>80.64</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -1758,32 +2049,68 @@
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
+      <c r="C6" s="6">
+        <v>16995</v>
+      </c>
+      <c r="D6" s="6">
+        <v>17005</v>
+      </c>
+      <c r="E6" s="6">
+        <v>3005</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2995</v>
+      </c>
+      <c r="G6" s="6">
+        <v>256</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.50314132425379199</v>
+      </c>
+      <c r="I6" s="6">
+        <v>75.98</v>
+      </c>
+      <c r="J6" s="6">
+        <v>99.9</v>
+      </c>
+      <c r="K6" s="6">
+        <v>86.31</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="C7" s="7">
+        <v>17068</v>
+      </c>
+      <c r="D7" s="7">
+        <v>16932</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2932</v>
+      </c>
+      <c r="F7" s="7">
+        <v>3068</v>
+      </c>
+      <c r="G7" s="7">
+        <v>64</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0.50757824946591101</v>
+      </c>
+      <c r="I7" s="7">
+        <v>75.3</v>
+      </c>
+      <c r="J7" s="7">
+        <v>99.92</v>
+      </c>
+      <c r="K7" s="7">
+        <v>85.88</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -1792,15 +2119,33 @@
       <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="C8" s="7">
+        <v>16994</v>
+      </c>
+      <c r="D8" s="7">
+        <v>17006</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3006</v>
+      </c>
+      <c r="F8" s="7">
+        <v>2994</v>
+      </c>
+      <c r="G8" s="7">
+        <v>128</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0.503015028669479</v>
+      </c>
+      <c r="I8" s="7">
+        <v>77.489999999999995</v>
+      </c>
+      <c r="J8" s="7">
+        <v>100</v>
+      </c>
+      <c r="K8" s="7">
+        <v>87.32</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
@@ -1809,15 +2154,33 @@
       <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+      <c r="C9" s="7">
+        <v>17013</v>
+      </c>
+      <c r="D9" s="7">
+        <v>16987</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2987</v>
+      </c>
+      <c r="F9" s="7">
+        <v>3013</v>
+      </c>
+      <c r="G9" s="7">
+        <v>32</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0.50408851006563604</v>
+      </c>
+      <c r="I9" s="7">
+        <v>72.64</v>
+      </c>
+      <c r="J9" s="7">
+        <v>99.98</v>
+      </c>
+      <c r="K9" s="7">
+        <v>84.15</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -1826,15 +2189,33 @@
       <c r="B10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
+      <c r="C10" s="7">
+        <v>17010</v>
+      </c>
+      <c r="D10" s="7">
+        <v>16990</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2990</v>
+      </c>
+      <c r="F10" s="7">
+        <v>3010</v>
+      </c>
+      <c r="G10" s="7">
+        <v>64</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0.504563963476647</v>
+      </c>
+      <c r="I10" s="7">
+        <v>68.319999999999993</v>
+      </c>
+      <c r="J10" s="7">
+        <v>99.74</v>
+      </c>
+      <c r="K10" s="7">
+        <v>81.11</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -1843,15 +2224,33 @@
       <c r="B11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="C11" s="8">
+        <v>16961</v>
+      </c>
+      <c r="D11" s="8">
+        <v>17039</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3039</v>
+      </c>
+      <c r="F11" s="8">
+        <v>2961</v>
+      </c>
+      <c r="G11" s="8">
+        <v>64</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.50205484825245805</v>
+      </c>
+      <c r="I11" s="8">
+        <v>69.52</v>
+      </c>
+      <c r="J11" s="8">
+        <v>99.78</v>
+      </c>
+      <c r="K11" s="8">
+        <v>81.95</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -1860,15 +2259,33 @@
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="C12" s="2">
+        <v>16984</v>
+      </c>
+      <c r="D12" s="2">
+        <v>17016</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3016</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2984</v>
+      </c>
+      <c r="G12" s="2">
+        <v>128</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.50250336765608805</v>
+      </c>
+      <c r="I12" s="2">
+        <v>82.34</v>
+      </c>
+      <c r="J12" s="2">
+        <v>99.82</v>
+      </c>
+      <c r="K12" s="2">
+        <v>90.24</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -1877,32 +2294,68 @@
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="C13" s="2">
+        <v>17073</v>
+      </c>
+      <c r="D13" s="2">
+        <v>16927</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2927</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3073</v>
+      </c>
+      <c r="G13" s="2">
+        <v>32</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.50800355381153905</v>
+      </c>
+      <c r="I13" s="2">
+        <v>82.47</v>
+      </c>
+      <c r="J13" s="2">
+        <v>100</v>
+      </c>
+      <c r="K13" s="2">
+        <v>90.39</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="C14" s="11">
+        <v>17006</v>
+      </c>
+      <c r="D14" s="11">
+        <v>16994</v>
+      </c>
+      <c r="E14" s="11">
+        <v>2994</v>
+      </c>
+      <c r="F14" s="11">
+        <v>3006</v>
+      </c>
+      <c r="G14" s="11">
+        <v>64</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0.50358334484886602</v>
+      </c>
+      <c r="I14" s="11">
+        <v>96.23</v>
+      </c>
+      <c r="J14" s="11">
+        <v>99.98</v>
+      </c>
+      <c r="K14" s="11">
+        <v>98.07</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -1911,15 +2364,33 @@
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="C15" s="2">
+        <v>17003</v>
+      </c>
+      <c r="D15" s="2">
+        <v>16997</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2997</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3003</v>
+      </c>
+      <c r="G15" s="2">
+        <v>128</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.50358334421477402</v>
+      </c>
+      <c r="I15" s="2">
+        <v>68.319999999999993</v>
+      </c>
+      <c r="J15" s="2">
+        <v>99.93</v>
+      </c>
+      <c r="K15" s="2">
+        <v>81.16</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -1928,15 +2399,33 @@
       <c r="B16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="C16" s="6">
+        <v>17008</v>
+      </c>
+      <c r="D16" s="6">
+        <v>16992</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2992</v>
+      </c>
+      <c r="F16" s="6">
+        <v>3008</v>
+      </c>
+      <c r="G16" s="6">
+        <v>32</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0.50446088881568696</v>
+      </c>
+      <c r="I16" s="6">
+        <v>67.319999999999993</v>
+      </c>
+      <c r="J16" s="6">
+        <v>99.93</v>
+      </c>
+      <c r="K16" s="6">
+        <v>80.44</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
